--- a/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__combo_fit_RV__Bliss_Score_RV.xlsx
+++ b/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__combo_fit_RV__Bliss_Score_RV.xlsx
@@ -376,560 +376,560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.07395603017158832</v>
+        <v>0.1961393253520207</v>
       </c>
       <c r="C2">
-        <v>0.05566414326825741</v>
+        <v>0.2481807389892114</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.08772409358694791</v>
+        <v>0.1717268235231545</v>
       </c>
       <c r="C3">
-        <v>0.07331853902561086</v>
+        <v>0.159984854153154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.05988219381370521</v>
+        <v>0.239827531021847</v>
       </c>
       <c r="C4">
-        <v>0.1044170085023454</v>
+        <v>0.1909981271231986</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.0708695921816419</v>
+        <v>0.02426467537525989</v>
       </c>
       <c r="C5">
-        <v>0.09758031853690528</v>
+        <v>0.2385725463827444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.239827531021847</v>
+        <v>0.03764007017189967</v>
       </c>
       <c r="C6">
-        <v>0.1909981271231986</v>
+        <v>0.08261409022409691</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.1717268235231545</v>
+        <v>0.1978472111208312</v>
       </c>
       <c r="C7">
-        <v>0.159984854153154</v>
+        <v>0.3686244808871806</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.1004755851212002</v>
+        <v>0.05473166069760534</v>
       </c>
       <c r="C8">
-        <v>0.3274832867236143</v>
+        <v>0.1088605711939522</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.1189265553048217</v>
+        <v>0.1262233812814038</v>
       </c>
       <c r="C9">
-        <v>0.277483621763939</v>
+        <v>0.278893283378097</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.08078912091320149</v>
+        <v>0.1703289370309194</v>
       </c>
       <c r="C10">
-        <v>0.1085909033062377</v>
+        <v>0.109786224314928</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.1978472111208312</v>
+        <v>0.07395603017158832</v>
       </c>
       <c r="C11">
-        <v>0.3686244808871806</v>
+        <v>0.05566414326825741</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.03764007017189967</v>
+        <v>0.2531141913196081</v>
       </c>
       <c r="C12">
-        <v>0.08261409022409691</v>
+        <v>0.1505981576740263</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.1961393253520207</v>
+        <v>0.1027929785387397</v>
       </c>
       <c r="C13">
-        <v>0.2481807389892114</v>
+        <v>0.1328102635401862</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.04320047781040215</v>
+        <v>0.01894598027570214</v>
       </c>
       <c r="C14">
-        <v>0.1632998197569655</v>
+        <v>0.04848891389081542</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.04967266137811554</v>
+        <v>0.03059688458505598</v>
       </c>
       <c r="C15">
-        <v>0.2689255426510147</v>
+        <v>0.03908156024763947</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.1795536422895545</v>
+        <v>0.1189265553048217</v>
       </c>
       <c r="C16">
-        <v>0.1756888082544352</v>
+        <v>0.277483621763939</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B17">
-        <v>0.0873219991279212</v>
+        <v>0.06380168761233436</v>
       </c>
       <c r="C17">
-        <v>0.4162243110657629</v>
+        <v>0.04571664798756402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.1703289370309194</v>
+        <v>0.06458492105311904</v>
       </c>
       <c r="C18">
-        <v>0.109786224314928</v>
+        <v>0.0575576918657131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.07044242371005274</v>
+        <v>0.09413319001756655</v>
       </c>
       <c r="C19">
-        <v>0.09607251606939188</v>
+        <v>0.2431107814845675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.1374423990589928</v>
+        <v>0.06067571309017384</v>
       </c>
       <c r="C20">
-        <v>0.08842816971620171</v>
+        <v>0.3942460685737097</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.06558134213657284</v>
+        <v>0.1895370351739109</v>
       </c>
       <c r="C21">
-        <v>0.06224185538616784</v>
+        <v>0.173212212813724</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.2531141913196081</v>
+        <v>0.08078912091320149</v>
       </c>
       <c r="C22">
-        <v>0.1505981576740263</v>
+        <v>0.1085909033062377</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.05473166069760534</v>
+        <v>0.05988219381370521</v>
       </c>
       <c r="C23">
-        <v>0.1088605711939522</v>
+        <v>0.1044170085023454</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.2188436325132497</v>
+        <v>0.0873219991279212</v>
       </c>
       <c r="C24">
-        <v>0.06929708746507272</v>
+        <v>0.4162243110657629</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.03946772009613202</v>
+        <v>0.107681296553713</v>
       </c>
       <c r="C25">
-        <v>0.05702467259839921</v>
+        <v>0.138133701703625</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.1633040978475205</v>
+        <v>0.03961108464205339</v>
       </c>
       <c r="C26">
-        <v>0.134400796798024</v>
+        <v>0.1685128987934263</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.1729701849179497</v>
+        <v>0.0708695921816419</v>
       </c>
       <c r="C27">
-        <v>0.1393467681427181</v>
+        <v>0.09758031853690528</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.107681296553713</v>
+        <v>0.1633040978475205</v>
       </c>
       <c r="C28">
-        <v>0.138133701703625</v>
+        <v>0.134400796798024</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.03961108464205339</v>
+        <v>0.04967266137811554</v>
       </c>
       <c r="C29">
-        <v>0.1685128987934263</v>
+        <v>0.2689255426510147</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.1027929785387397</v>
+        <v>0.0675844474128116</v>
       </c>
       <c r="C30">
-        <v>0.1328102635401862</v>
+        <v>0.04161958196766227</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.01894598027570214</v>
+        <v>0.1004755851212002</v>
       </c>
       <c r="C31">
-        <v>0.04848891389081542</v>
+        <v>0.3274832867236143</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.06458492105311904</v>
+        <v>0.06513182680150686</v>
       </c>
       <c r="C32">
-        <v>0.0575576918657131</v>
+        <v>0.1351732021272145</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.0675844474128116</v>
+        <v>0.07044242371005274</v>
       </c>
       <c r="C33">
-        <v>0.04161958196766227</v>
+        <v>0.09607251606939188</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.11280128342019</v>
+        <v>0.04320047781040215</v>
       </c>
       <c r="C34">
-        <v>0.1065516418762605</v>
+        <v>0.1632998197569655</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.06513182680150686</v>
+        <v>0.06558134213657284</v>
       </c>
       <c r="C35">
-        <v>0.1351732021272145</v>
+        <v>0.06224185538616784</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.03059688458505598</v>
+        <v>0.08772409358694791</v>
       </c>
       <c r="C36">
-        <v>0.03908156024763947</v>
+        <v>0.07331853902561086</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.06067571309017384</v>
+        <v>0.11280128342019</v>
       </c>
       <c r="C37">
-        <v>0.3942460685737097</v>
+        <v>0.1065516418762605</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.09413319001756655</v>
+        <v>0.1795536422895545</v>
       </c>
       <c r="C38">
-        <v>0.2431107814845675</v>
+        <v>0.1756888082544352</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.133477232160546</v>
+        <v>0.1483979773814767</v>
       </c>
       <c r="C39">
-        <v>0.08846752025045179</v>
+        <v>0.1419353754773581</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.1483979773814767</v>
+        <v>0.2188436325132497</v>
       </c>
       <c r="C40">
-        <v>0.1419353754773581</v>
+        <v>0.06929708746507272</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.06380168761233436</v>
+        <v>0.133477232160546</v>
       </c>
       <c r="C41">
-        <v>0.04571664798756402</v>
+        <v>0.08846752025045179</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.02426467537525989</v>
+        <v>0.1374423990589928</v>
       </c>
       <c r="C42">
-        <v>0.2385725463827444</v>
+        <v>0.08842816971620171</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.1895370351739109</v>
+        <v>0.03946772009613202</v>
       </c>
       <c r="C43">
-        <v>0.173212212813724</v>
+        <v>0.05702467259839921</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.1262233812814038</v>
+        <v>0.1729701849179497</v>
       </c>
       <c r="C44">
-        <v>0.278893283378097</v>
+        <v>0.1393467681427181</v>
       </c>
     </row>
   </sheetData>
@@ -957,7 +957,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1017,7 +1017,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1029,7 +1029,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1173,7 +1173,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1197,7 +1197,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1305,7 +1305,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1365,7 +1365,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1413,7 +1413,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1437,7 +1437,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
